--- a/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/RSQ_COMPLETE_QUALITATIVE_CODING_20260825_142706.xlsx
+++ b/Code_Digital_Capabilities_Risk_Intelligence_Orchestration_Resilience_Model_4/RSQ_COMPLETE_QUALITATIVE_CODING_20260825_142706.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="11_E8B46983672C599191A717EB7E9F7357D53BB327" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90628978-5B88-46DC-B489-675A9F7A86A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Original_RSQ" sheetId="1" r:id="rId1"/>
